--- a/Group2_23130238_VuChauHoaiPhong.xlsx
+++ b/Group2_23130238_VuChauHoaiPhong.xlsx
@@ -526,9 +526,6 @@
     <t>Màu áo tự thay đổi theo màu biến thể đã chọn</t>
   </si>
   <si>
-    <t>Search_Exact_0</t>
-  </si>
-  <si>
     <t>Ảo chuyển từ sản phẩm gốc màu xanh sang đỏ như đã chọn.</t>
   </si>
   <si>
@@ -570,6 +567,9 @@
   </si>
   <si>
     <t>Hệ thống nhận diện từ đồng nghĩa 'Coat' và trả về các sản phẩm 'Jacket' có mức giá từ $10.00 - $49.99</t>
+  </si>
+  <si>
+    <t>UNTESTED</t>
   </si>
   <si>
     <t>Chưa kiểm thử (Untested) - Chờ Backend Admin hoàn tất cấu hình từ đồng nghĩa (Search Synonyms).</t>
@@ -791,7 +791,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,6 +838,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
         <bgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1178,7 +1184,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1202,16 +1208,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1220,89 +1226,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1340,7 +1346,10 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2261,7 +2270,7 @@
         <v>117</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>13</v>
@@ -2270,53 +2279,53 @@
         <v>14</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" ht="96.6" spans="1:8">
       <c r="A23" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" ht="110.4" spans="1:8">
       <c r="A24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>13</v>
+      <c r="F24" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>14</v>
@@ -2341,7 +2350,7 @@
       <c r="E25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="14" t="s">
         <v>36</v>
       </c>
       <c r="G25" s="2" t="s">
